--- a/data/season_2026/next_games/next_games.xlsx
+++ b/data/season_2026/next_games/next_games.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T66"/>
+  <dimension ref="A1:T118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,75 +531,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Super League - GRC SL</t>
+          <t>La Liga - ESP PL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Panathinaikos vs Panaitolikos</t>
+          <t>Elche vs Real Madrid</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-13 18:30:00</t>
+          <t>2026-09-15 19:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>12.00</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>1.20</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>12.00</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14.39</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr">
         <is>
           <t>https://www.quantumodds.xyz/</t>
@@ -609,305 +617,217 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Serie A - ITA SA</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sassuolo vs Juventus</t>
+          <t>Boyacá Chicó vs Alianza Petrolera</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-13 18:45:00</t>
+          <t>2026-09-16 00:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ligue 1 - FRA L1</t>
+          <t>Liga MX - MEX AL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Brest vs Paris Saint Germain</t>
+          <t>Puebla vs Toluca</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-13 18:45:00</t>
+          <t>2026-09-16 01:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.81</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>Premier League - None</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mirassol vs Vitória</t>
+          <t>Rodina Moskva vs Rubin Kazan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-13 19:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
+          <t>2026-09-16 15:30:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.41</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Premier League - None</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deportivo Pereira vs Atlético Bucaramanga</t>
+          <t>Spartak Moskva vs Fakel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-13 19:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
+          <t>2026-09-16 15:30:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
+          <t>8.97</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -926,52 +846,52 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Real Sociedad vs Atlético de Madrid</t>
+          <t>Deportivo A Coruña vs Sevilla</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-13 19:00:00</t>
+          <t>2026-09-16 17:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -987,62 +907,70 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>La Liga - ESP PL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tenerife vs Leganés</t>
+          <t>Atlético de Madrid vs Osasuna</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-13 19:00:00</t>
+          <t>2026-09-16 17:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
@@ -1053,59 +981,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>Premier League - None</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Defensor Sporting vs Deportivo Maldonado</t>
+          <t>Lokomotiv Moskva vs Krylya Sovetov</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-13 19:00:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
+          <t>2026-09-16 17:45:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+          <t>3.89</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1119,310 +1027,274 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Liga Portugal - PRT PL</t>
+          <t>Premier League - None</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Famalicão vs Sporting CP</t>
+          <t>Baltika Kaliningrad vs Zenit</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-13 19:30:00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
+          <t>2026-09-16 17:45:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>2.04</t>
-        </is>
-      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>La Liga - ESP PL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Argentinos Juniors vs Gimnasia La Plata</t>
+          <t>Levante vs Athletic Club</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-13 20:00:00</t>
+          <t>2026-09-16 19:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>2.05</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>La Liga - ESP PL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Flamengo vs Corinthians</t>
+          <t>FC Barcelona vs Racing Santander</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-09-13 20:30:00</t>
+          <t>2026-09-16 19:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>18.71</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Atlético Nacional vs Rionegro Águilas</t>
+          <t>Botafogo vs Grêmio</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-09-13 21:05:00</t>
+          <t>2026-09-16 22:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -1431,294 +1303,270 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chicago Fire vs New England</t>
+          <t>Once Caldas vs Deportes Tolima</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-09-13 21:30:00</t>
+          <t>2026-09-16 23:15:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>3.80</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>3.87</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Independiente vs San Lorenzo</t>
+          <t>Internacional de Bogotá vs Atlético Nacional</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-09-13 22:15:00</t>
+          <t>2026-09-17 01:20:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>Premier League - None</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps vs Austin</t>
+          <t>Orenburg vs Krasnodar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-09-13 22:30:00</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>8.50</t>
-        </is>
-      </c>
+          <t>2026-09-17 13:15:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>9.64</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
         <is>
           <t>1.80</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>2.04</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>Premier League - None</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Peñarol vs Albion</t>
+          <t>Akron vs Akhmat Grozny</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-09-13 22:30:00</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
+          <t>2026-09-17 15:30:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7.34</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
@@ -1727,123 +1575,111 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Premier League - None</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Once Caldas vs Deportivo Cali</t>
+          <t>Rostov vs Dinamo Moskva</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-09-13 23:10:00</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
+          <t>2026-09-17 15:30:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3.86</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>La Liga - ESP PL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Huracán vs Racing Club</t>
+          <t>Real Betis vs Getafe</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-09-14 00:30:00</t>
+          <t>2026-09-17 17:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1859,123 +1695,111 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>Premier League - None</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>San Diego vs Philadelphia Union</t>
+          <t>Dynamo Makhachkala vs CSKA Moskva</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-09-14 01:00:00</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
+          <t>2026-09-17 17:45:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.39</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Liga MX - MEX AL</t>
+          <t>La Liga - ESP PL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Santos Laguna vs Juárez</t>
+          <t>Málaga vs Villarreal</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-09-14 01:00:00</t>
+          <t>2026-09-17 19:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1991,57 +1815,57 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Liga MX - MEX AL</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Guadalajara vs Pumas UNAM</t>
+          <t>Atlético Bucaramanga vs Independiente Medellín</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-09-14 01:07:00</t>
+          <t>2026-09-17 23:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -2057,303 +1881,255 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>2. Bundesliga - GER BII</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cúcuta Deportivo vs Millonarios</t>
+          <t>SpVgg Greuther Fürth vs Magdeburg</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-09-14 01:15:00</t>
+          <t>2026-09-18 16:30:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2.04</t>
-        </is>
-      </c>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
+      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Serie A - ITA SA</t>
+          <t>2. Bundesliga - GER BII</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Torino vs Roma</t>
+          <t>VfL Wolfsburg vs Darmstadt 98</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-09-14 16:30:00</t>
+          <t>2026-09-18 16:30:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>2.04</t>
-        </is>
-      </c>
+      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Serie A - ITA SA</t>
+          <t>Superliga - DNK SL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Como vs Parma</t>
+          <t>Lyngby Boldklub vs Silkeborg IF</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-09-14 16:30:00</t>
+          <t>2026-09-18 17:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>14.50</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2.37</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
+      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
+      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Superliga - DNK SL</t>
+          <t>Super Lig - TUR SL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FC Midtjylland vs Brøndby IF</t>
+          <t>Kasımpaşa vs Konyaspor</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-09-14 17:00:00</t>
+          <t>2026-09-18 17:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -2369,57 +2145,57 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Liga Portugal 2 - PRT SL</t>
+          <t>Eredivisie - NLD E</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sporting CP II vs Lusitania FC Lourosa</t>
+          <t>FC Groningen vs PEC Zwolle</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-09-14 17:00:00</t>
+          <t>2026-09-18 18:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -2435,146 +2211,146 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Liga Portugal 2 - PRT SL</t>
+          <t>Bundesliga - GER BI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Porto II vs Vizela</t>
+          <t>FC Bayern München vs FC Union Berlin</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-09-14 17:00:00</t>
+          <t>2026-09-18 18:30:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>1.80</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>1.90</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
+      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
+      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Super Lig - TUR SL</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Gaziantep F.K. vs Fenerbahçe</t>
+          <t>Albacete vs Córdoba</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-09-14 17:00:00</t>
+          <t>2026-09-18 18:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t>1.80</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="S29" t="inlineStr"/>
@@ -2583,80 +2359,80 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Liga Portugal - PRT PL</t>
+          <t>Serie A - ITA SA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rio Ave vs Estrela Amadora</t>
+          <t>Monza vs Sassuolo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-09-14 17:45:00</t>
+          <t>2026-09-18 18:45:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
@@ -2665,57 +2441,57 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Ligue 1 - FRA L1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Celta Fortuna vs SD Eibar</t>
+          <t>Monaco vs Lens</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-09-14 18:30:00</t>
+          <t>2026-09-18 18:45:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>3.40</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
           <t>3.76</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -2731,66 +2507,74 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Serie A - ITA SA</t>
+          <t>Pro League - BEL FDA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Inter vs Udinese</t>
+          <t>Gent vs Standard Liège</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-09-14 18:45:00</t>
+          <t>2026-09-18 18:45:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
       <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
     </row>
@@ -2802,77 +2586,61 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Leeds United vs Newcastle United</t>
+          <t>Brentford vs Chelsea</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-09-14 19:00:00</t>
+          <t>2026-09-18 19:00:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
+      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
+      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
     </row>
@@ -2884,118 +2652,134 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Villarreal vs Real Betis</t>
+          <t>Espanyol vs Elche</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-09-14 19:00:00</t>
+          <t>2026-09-18 19:00:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>4.65</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
           <t>1.90</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>3.95</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>3.74</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2.37</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Liga Portugal - PRT PL</t>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Moreirense vs Marítimo</t>
+          <t>Central Cordoba SdE vs Defensa y Justicia</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:00</t>
+          <t>2026-09-18 21:00:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
           <t>2.90</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -3011,27 +2795,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Liga Portugal - PRT PL</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sporting Braga vs Estoril</t>
+          <t>Rionegro Águilas vs Deportivo Pereira</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-09-14 19:45:00</t>
+          <t>2026-09-18 21:00:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3041,93 +2825,109 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
           <t>1.90</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>Major League Soccer - USA MLS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Banfield vs Barracas Central</t>
+          <t>New York City vs New York RB</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-09-14 22:00:00</t>
+          <t>2026-09-18 23:30:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -3148,52 +2948,52 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Deportivo Riestra vs Lanús</t>
+          <t>Racing Club vs Sarmiento</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-09-14 22:00:00</t>
+          <t>2026-09-19 00:15:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -3209,152 +3009,116 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>Liga MX - MEX AL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Montevideo City Torque vs Liverpool</t>
+          <t>Puebla vs Atlante</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-09-14 22:00:00</t>
+          <t>2026-09-19 01:00:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t>3.25</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>3.36</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
+      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
+      <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>Liga MX - MEX AL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bahia vs Remo</t>
+          <t>Juárez vs Tigres UANL</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-09-14 23:00:00</t>
+          <t>2026-09-19 03:00:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
@@ -3365,146 +3129,162 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>K League 1 - KOR KL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Instituto vs Estudiantes de Río Cuarto</t>
+          <t>Bucheon 1995 vs Gimcheon Sangmu</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-09-15 00:15:00</t>
+          <t>2026-09-19 07:30:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2.62</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
       <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>J1 League - JPN JL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>América de Cali vs Deportivo Pasto</t>
+          <t>Avispa Fukuoka vs Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-09-15 01:00:00</t>
+          <t>2026-09-19 09:00:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="S42" t="inlineStr"/>
@@ -3513,489 +3293,493 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Liga MX - MEX AL</t>
+          <t>J1 League - JPN JL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>León vs Atlético San Luis</t>
+          <t>Kawasaki Frontale vs Kashima Antlers</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-09-15 01:00:00</t>
+          <t>2026-09-19 09:00:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
+      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
+      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>La Liga - ESP PL</t>
+          <t>J1 League - JPN JL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Rayo Vallecano vs Espanyol</t>
+          <t>V-Varen Nagasaki vs Cerezo Osaka</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-09-15 17:00:00</t>
+          <t>2026-09-19 09:30:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3.66</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
           <t>2.10</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>2.14</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>3.56</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
+      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
+      <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Eredivisie - NLD E</t>
+          <t>J1 League - JPN JL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ajax vs Willem II</t>
+          <t>Shimizu S-Pulse vs JEF United</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-09-15 18:00:00</t>
+          <t>2026-09-19 09:30:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>11.70</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr"/>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
       <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>La Liga - ESP PL</t>
+          <t>J1 League - JPN JL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Deportivo Alavés vs Valencia</t>
+          <t>Urawa Reds vs Tokyo Verdy</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-09-15 18:00:00</t>
+          <t>2026-09-19 09:30:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>La Liga - ESP PL</t>
+          <t>K League 1 - KOR KL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Elche vs Real Madrid</t>
+          <t>Anyang vs Ulsan HD</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-09-15 19:30:00</t>
+          <t>2026-09-19 10:00:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
+      <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>J1 League - JPN JL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Boyacá Chicó vs Alianza Petrolera</t>
+          <t>Fagiano Okayama vs Kyoto Sanga</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-09-16 00:30:00</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
+          <t>2026-09-19 10:00:00</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2.91</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Liga MX - MEX AL</t>
+          <t>J1 League - JPN JL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Puebla vs Toluca</t>
+          <t>FC Tokyo vs Nagoya Grampus</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-09-16 01:00:00</t>
+          <t>2026-09-19 10:00:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -4011,39 +3795,59 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Premier League - None</t>
+          <t>J1 League - JPN JL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Rodina Moskva vs Rubin Kazan</t>
+          <t>Yokohama F. Marinos vs Mito Hollyhock</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-09-16 15:30:00</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+          <t>2026-09-19 10:30:00</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2.44</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -4057,39 +3861,59 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Premier League - None</t>
+          <t>2. Bundesliga - GER BII</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Spartak Moskva vs Fakel</t>
+          <t>Holstein Kiel vs Osnabrück</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-09-16 15:30:00</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+          <t>2026-09-19 11:00:00</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>8.60</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+          <t>4.31</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
@@ -4103,43 +3927,71 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>La Liga - ESP PL</t>
+          <t>2. Bundesliga - GER BII</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Deportivo A Coruña vs Sevilla</t>
+          <t>Karlsruher SC vs Nürnberg</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-09-16 17:00:00</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+          <t>2026-09-19 11:00:00</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>3.16</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
@@ -4149,70 +4001,62 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>La Liga - ESP PL</t>
+          <t>2. Bundesliga - GER BII</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Atlético de Madrid vs Osasuna</t>
+          <t>Kaiserslautern vs Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-09-16 17:00:00</t>
+          <t>2026-09-19 11:00:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
@@ -4223,42 +4067,70 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Premier League - None</t>
+          <t>Premier League - UK PL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva vs Krylya Sovetov</t>
+          <t>Tottenham Hotspur vs Aston Villa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-09-16 17:45:00</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+          <t>2026-09-19 11:30:00</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>3.94</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
@@ -4269,39 +4141,59 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Premier League - None</t>
+          <t>La Liga - ESP PL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Baltika Kaliningrad vs Zenit</t>
+          <t>Osasuna vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-09-16 17:45:00</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+          <t>2026-09-19 12:00:00</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
@@ -4315,80 +4207,80 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>La Liga - ESP PL</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Levante vs Athletic Club</t>
+          <t>Real Sociedad II vs Mallorca</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-09-16 19:30:00</t>
+          <t>2026-09-19 12:00:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="S56" t="inlineStr"/>
@@ -4397,57 +4289,57 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>La Liga - ESP PL</t>
+          <t>Serie A - ITA SA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FC Barcelona vs Racing Santander</t>
+          <t>Udinese vs Cagliari</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-09-16 19:30:00</t>
+          <t>2026-09-19 13:00:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>25.06</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -4463,80 +4355,80 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>Serie A - ITA SA</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Botafogo vs Grêmio</t>
+          <t>Bologna vs Torino</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-09-16 22:30:00</t>
+          <t>2026-09-19 13:00:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="S58" t="inlineStr"/>
@@ -4545,109 +4437,125 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Bundesliga - GER BI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Once Caldas vs Deportes Tolima</t>
+          <t>Werder Bremen vs FC Augsburg</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-09-16 23:15:00</t>
+          <t>2026-09-19 13:30:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
+      <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
+      <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Bundesliga - GER BI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá vs Atlético Nacional</t>
+          <t>Hamburger SV vs FC Köln</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-09-17 01:20:00</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
+          <t>2026-09-19 13:30:00</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
@@ -4661,39 +4569,59 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Premier League - None</t>
+          <t>Bundesliga - GER BI</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Orenburg vs Krasnodar</t>
+          <t>Borussia Mönchengladbach vs FSV Mainz 05</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-09-17 13:15:00</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
+          <t>2026-09-19 13:30:00</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
@@ -4707,226 +4635,294 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Premier League - None</t>
+          <t>Bundesliga - GER BI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Akron vs Akhmat Grozny</t>
+          <t>Eintracht Frankfurt vs SC Freiburg</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-09-17 15:30:00</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
+          <t>2026-09-19 13:30:00</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
+      <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
+      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Premier League - None</t>
+          <t>Premier League - UK PL</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Rostov vs Dinamo Moskva</t>
+          <t>Newcastle United vs Hull City</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-09-17 15:30:00</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
+          <t>2026-09-19 14:00:00</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2.43</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+          <t>5.23</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
+      <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
+      <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>La Liga - ESP PL</t>
+          <t>Premier League - UK PL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Real Betis vs Getafe</t>
+          <t>Everton vs Ipswich Town</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-09-17 17:00:00</t>
+          <t>2026-09-19 14:00:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t>1.66</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
       <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
       <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Premier League - None</t>
+          <t>Premier League - UK PL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Dynamo Makhachkala vs CSKA Moskva</t>
+          <t>Brighton &amp; Hove Albion vs Arsenal</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-09-17 17:45:00</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
+          <t>2026-09-19 14:00:00</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2.29</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="S65" t="inlineStr"/>
@@ -4935,68 +4931,3740 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>La Liga - ESP PL</t>
+          <t>Pro League - BEL FDA</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Málaga vs Villarreal</t>
+          <t>OH Leuven vs La Louvière</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-09-17 19:30:00</t>
+          <t>2026-09-19 14:00:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
           <t>1.95</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>3.58</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>3.98</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Super Lig - TUR SL</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Kocaelispor vs Gaziantep F.K.</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-09-19 14:00:00</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Super Lig - TUR SL</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Çorum FK vs Alanyaspor</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-09-19 14:00:00</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>3.63</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>La Liga - ESP PL</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Athletic Club vs Deportivo Alavés</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-09-19 14:15:00</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>3.97</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>5.34</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>La Liga 2 - ESP S</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>FC Andorra vs Sporting Gijón</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-09-19 14:15:00</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>3.53</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>3.58</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Eredivisie - NLD E</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ADO Den Haag vs SC Cambuur</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-09-19 14:30:00</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>4.21</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Liga Portugal - PRT PL</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Nacional vs Famalicão</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-09-19 14:30:00</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>3.63</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Liga Portugal - PRT PL</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Gil Vicente vs Marítimo</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-09-19 14:30:00</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Ligue 1 - FRA L1</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Paris vs Strasbourg</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-09-19 15:15:00</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>3.71</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Serie A - ITA SA</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Roma vs Inter</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-09-19 16:00:00</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Superliga - DNK SL</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Odense BK vs FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-09-19 16:00:00</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>3.92</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>4.18</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Super League - GRC SL</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Atromitos vs Kifisia</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-09-19 16:00:00</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Pro League - BEL FDA</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Sporting Charleroi vs Cercle Brugge</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-09-19 16:15:00</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>4.32</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>3.97</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Premier League - UK PL</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Nottingham Forest vs Coventry City</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-09-19 16:30:00</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>5.19</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>La Liga - ESP PL</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Celta de Vigo vs Racing Santander</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-09-19 16:30:00</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Bundesliga - GER BI</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>VfB Stuttgart vs Borussia Dortmund</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-09-19 16:30:00</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>La Liga 2 - ESP S</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Eldense vs SD Eibar</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-09-19 16:30:00</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2.92</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>La Liga 2 - ESP S</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Castellón vs Tenerife</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-09-19 16:30:00</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>5.53</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Super League - GRC SL</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Aris vs Iraklis Thessaloniki</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-09-19 16:30:00</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>3.81</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>5.44</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Eredivisie - NLD E</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Sparta Rotterdam vs SC Heerenveen</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-09-19 16:45:00</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>3.69</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Liga Portugal - PRT PL</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Alverca vs Rio Ave</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-09-19 17:00:00</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>3.58</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Super Lig - TUR SL</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>İstanbul Başakşehir vs Gençlerbirliği</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-09-19 17:00:00</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>4.45</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>5.87</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Super Lig - TUR SL</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Trabzonspor vs Galatasaray</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-09-19 17:00:00</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Gimnasia La Plata vs Banfield</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-09-19 17:30:00</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>3.59</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>4.49</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Gimnasia y Esgrima Mendoza vs Deportivo Riestra</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-09-19 17:30:00</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>3.93</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Eredivisie - NLD E</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Ajax vs Excelsior</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-09-19 18:00:00</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>6.36</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>8.82</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2. Bundesliga - GER BII</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Dynamo Dresden vs Hertha BSC</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-09-19 18:30:00</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>4.21</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Serie A - ITA SA</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Venezia vs Lazio</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-09-19 18:45:00</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>3.79</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Ligue 1 - FRA L1</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Toulouse vs Le Havre</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-09-19 18:45:00</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Ligue 1 - FRA L1</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Olympique Lyonnais vs Rennes</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-09-19 18:45:00</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Ligue 1 - FRA L1</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Le Mans vs Lorient</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-09-19 18:45:00</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>3.46</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Ligue 1 - FRA L1</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Angers SCO vs Troyes</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-09-19 18:45:00</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Pro League - BEL FDA</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Lommel SK vs Mechelen</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-09-19 18:45:00</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Pro League - BEL FDA</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Anderlecht vs Zulte-Waregem</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-09-19 18:45:00</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>4.42</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Serie A - BRA CB</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro vs Chapecoense</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-09-19 19:00:00</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>4.67</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>7.43</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Liga BetPlay - COL PA</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Millonarios vs Boyacá Chicó</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-09-19 19:00:00</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
+      <c r="S101" t="inlineStr"/>
+      <c r="T101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Eredivisie - NLD E</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Willem II vs Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-09-19 19:00:00</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>3.79</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>La Liga - ESP PL</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Sevilla vs FC Barcelona</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-09-19 19:00:00</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>11.65</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>6.33</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr"/>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>La Liga 2 - ESP S</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Cádiz vs Girona</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-09-19 19:00:00</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>3.79</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr"/>
+      <c r="T104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Liga Portugal - PRT PL</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Sporting CP vs Arouca</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-09-19 19:30:00</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>4.46</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>10.98</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr"/>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Unión Santa Fe vs Independiente</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-09-19 19:45:00</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
+      <c r="S106" t="inlineStr"/>
+      <c r="T106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Serie A - BRA CB</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Mirassol vs Botafogo</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-09-19 20:00:00</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr"/>
+      <c r="S107" t="inlineStr"/>
+      <c r="T107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Liga BetPlay - COL PA</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Alianza Petrolera vs Santa Fe</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-09-19 21:05:00</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
+      <c r="S108" t="inlineStr"/>
+      <c r="T108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Serie A - BRA CB</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Remo vs Santos</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-09-19 21:30:00</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr"/>
+      <c r="T109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>River Plate vs Huracán</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-09-19 22:00:00</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>3.83</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>7.03</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Liga MX - MEX AL</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Atlético San Luis vs Necaxa</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-09-19 23:00:00</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr"/>
+      <c r="S111" t="inlineStr"/>
+      <c r="T111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Liga MX - MEX AL</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Atlas vs Pumas UNAM</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-09-19 23:00:00</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr"/>
+      <c r="T112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Liga BetPlay - COL PA</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Deportivo Cali vs Cúcuta Deportivo</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026-09-19 23:10:00</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>3.94</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>6.83</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr"/>
+      <c r="T113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Major League Soccer - USA MLS</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>SJ Earthquakes vs Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026-09-19 23:30:00</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>3.89</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr"/>
+      <c r="S114" t="inlineStr"/>
+      <c r="T114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Major League Soccer - USA MLS</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>CF Montréal vs Columbus Crew</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2026-09-19 23:30:00</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>3.71</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr"/>
+      <c r="T115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Major League Soccer - USA MLS</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>New England vs Orlando City</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2026-09-19 23:30:00</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>3.78</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr"/>
+      <c r="T116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Major League Soccer - USA MLS</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>DC United vs Charlotte</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2026-09-19 23:30:00</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr"/>
+      <c r="T117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Serie A - BRA CB</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Vasco da Gama vs Coritiba</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2026-09-19 23:30:00</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>5.92</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr"/>
+      <c r="T118" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/data/season_2026/next_games/next_games.xlsx
+++ b/data/season_2026/next_games/next_games.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:T51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,20 +489,40 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>Bet365_Lines_Goals_Over_3.5</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>Bet365_Lines_Goals_Under_2.5</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Bet365_Lines_Goals_Under_3.5</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
         <is>
           <t>Pinnacle_Lines_Goals_Over_2.5</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Pinnacle_Lines_Goals_Over_3.5</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
         <is>
           <t>Pinnacle_Lines_Goals_Under_2.5</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Pinnacle_Lines_Goals_Under_3.5</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
         <is>
           <t>Para mais mercados visite o site</t>
         </is>
@@ -511,64 +531,84 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Barracas Central vs Independiente Rivadavia</t>
+          <t>América de Cali vs Rionegro Águilas</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:00:00</t>
+          <t>2026-09-24 00:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t>https://www.quantumodds.xyz/</t>
         </is>
@@ -577,57 +617,57 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>Major League Soccer - USA MLS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Central Español vs Montevideo City Torque</t>
+          <t>Seattle Sounders vs Real Salt Lake</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:00</t>
+          <t>2026-09-24 01:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -635,138 +675,158 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lanús vs Estudiantes</t>
+          <t>Atlético Nacional vs Millonarios</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-22 00:15:00</t>
+          <t>2026-09-25 00:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Independiente Medellín vs Jaguares de Córdoba</t>
+          <t>Girona vs Albacete</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-22 23:00:00</t>
+          <t>2026-09-25 18:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -776,52 +836,52 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Santa Fe vs Deportivo Cali</t>
+          <t>Boyacá Chicó vs Deportivo Pasto</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-23 01:00:00</t>
+          <t>2026-09-25 23:10:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -829,61 +889,65 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Liga MX - MEX AL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>América de Cali vs Rionegro Águilas</t>
+          <t>Atlante vs Monterrey</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-24 00:30:00</t>
+          <t>2026-09-26 01:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -891,61 +955,65 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Seattle Sounders vs Real Salt Lake</t>
+          <t>Once Caldas vs Atlético Bucaramanga</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-24 01:30:00</t>
+          <t>2026-09-26 01:15:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -953,84 +1021,92 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Liga MX - MEX AL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Atlético Nacional vs Millonarios</t>
+          <t>Tijuana vs Atlas</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-25 00:30:00</t>
+          <t>2026-09-26 03:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr"/>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1040,114 +1116,126 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Girona vs Albacete</t>
+          <t>Ceuta vs Real Sociedad II</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-25 18:30:00</t>
+          <t>2026-09-26 12:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Primera Division - URY CL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Boyacá Chicó vs Deportivo Pasto</t>
+          <t>Atlético Progreso vs Racing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-25 23:10:00</t>
+          <t>2026-09-26 14:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1155,10 +1243,2746 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>La Liga 2 - ESP S</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Granada vs FC Andorra</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-09-26 14:15:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>La Liga 2 - ESP S</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Tenerife vs Cádiz</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-09-26 16:30:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>La Liga 2 - ESP S</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Celta Fortuna vs Sabadell</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-09-26 16:30:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Primera Division - URY CL</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cerro Largo vs Nacional</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-09-26 18:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>3.57</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Liga BetPlay - COL PA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Deportivo Pereira vs Internacional de Bogotá</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-09-26 21:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Primera Division - URY CL</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Peñarol vs Boston River</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-09-26 21:30:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>4.63</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>7.32</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Liga MX - MEX AL</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Cruz Azul vs Toluca</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-09-26 22:50:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2.73</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Liga MX - MEX AL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Guadalajara vs Querétaro</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-09-26 23:07:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>5.11</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7.12</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Liga BetPlay - COL PA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Cúcuta Deportivo vs Llaneros</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-09-26 23:15:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Major League Soccer - USA MLS</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Philadelphia Union vs Orlando City</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-09-26 23:30:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>5.26</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5.87</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Major League Soccer - USA MLS</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Atlanta United vs New York City</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-09-26 23:30:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Major League Soccer - USA MLS</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CF Montréal vs Cincinnati</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-09-26 23:30:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3.84</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Major League Soccer - USA MLS</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Charlotte vs Chicago Fire</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-09-26 23:30:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Major League Soccer - USA MLS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>New York RB vs St. Louis City</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-09-26 23:30:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Major League Soccer - USA MLS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dallas vs Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-09-27 00:30:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Major League Soccer - USA MLS</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Seattle Sounders vs Minnesota United</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-09-27 00:30:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Major League Soccer - USA MLS</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Nashville SC vs Toronto</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-09-27 00:30:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>6.01</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Major League Soccer - USA MLS</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Austin vs San Diego</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-09-27 00:30:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>3.58</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Major League Soccer - USA MLS</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Houston Dynamo vs Sporting KC</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-09-27 00:30:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>4.64</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5.94</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Primera Division - URY CL</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Montevideo City Torque vs Deportivo Maldonado</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-09-27 00:30:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Liga BetPlay - COL PA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Junior FC vs Independiente Medellín</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:20:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Major League Soccer - USA MLS</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Real Salt Lake vs New England</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-09-27 01:30:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Major League Soccer - USA MLS</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>LA Galaxy vs Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-09-27 02:30:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Major League Soccer - USA MLS</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs DC United</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-09-27 02:30:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>6.54</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>9.71</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Major League Soccer - USA MLS</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SJ Earthquakes vs Portland Timbers</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-09-27 02:30:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Liga MX - MEX AL</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Santos Laguna vs Pachuca</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-09-27 03:05:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Liga MX - MEX AL</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Puebla</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-09-27 03:10:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>4.55</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>5.39</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>K League 1 - KOR KL</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Gangwon vs Incheon United</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-09-27 10:00:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>La Liga 2 - ESP S</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Real Valladolid vs Córdoba</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-09-27 12:00:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primera Division - URY CL</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Central Español vs Liverpool</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-09-27 14:00:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>4.19</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>La Liga 2 - ESP S</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Mallorca vs Almería</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-09-27 14:15:00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>La Liga 2 - ESP S</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SD Eibar vs Las Palmas</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-09-27 16:30:00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>La Liga 2 - ESP S</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Burgos vs Eldense</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-09-27 16:30:00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Liga MX - MEX AL</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Pumas UNAM vs Atlético San Luis</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-09-27 18:00:00</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>3.66</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3.66</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Primera Division - URY CL</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Juventud vs Cerro</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-09-27 18:00:00</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4.85</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>La Liga 2 - ESP S</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Real Oviedo vs Sporting Gijón</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-09-27 19:00:00</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3.98</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Liga BetPlay - COL PA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Jaguares de Córdoba vs Alianza Petrolera</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-09-27 21:00:00</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Primera Division - URY CL</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Defensor Sporting vs Danubio</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-09-27 21:00:00</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Major League Soccer - USA MLS</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Columbus Crew vs Inter Miami</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:00:00</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Liga BetPlay - COL PA</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Fortaleza CEIF vs Deportes Tolima</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:05:00</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/season_2026/next_games/next_games.xlsx
+++ b/data/season_2026/next_games/next_games.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T51"/>
+  <dimension ref="A1:T54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,83 +531,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>América de Cali vs Rionegro Águilas</t>
+          <t>Girona vs Albacete</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-24 00:30:00</t>
+          <t>2026-09-25 18:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>1.80</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr"/>
+          <t>5.28</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr"/>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr">
         <is>
           <t>https://www.quantumodds.xyz/</t>
@@ -617,57 +617,57 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Seattle Sounders vs Real Salt Lake</t>
+          <t>Boyacá Chicó vs Deportivo Pasto</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-24 01:30:00</t>
+          <t>2026-09-25 23:10:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -683,22 +683,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Liga MX - MEX AL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Atlético Nacional vs Millonarios</t>
+          <t>Atlante vs Monterrey</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-25 00:30:00</t>
+          <t>2026-09-26 01:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -723,99 +723,83 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Girona vs Albacete</t>
+          <t>Once Caldas vs Atlético Bucaramanga</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-25 18:30:00</t>
+          <t>2026-09-26 01:15:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>4.20</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -831,113 +815,129 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Liga MX - MEX AL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Boyacá Chicó vs Deportivo Pasto</t>
+          <t>Tijuana vs Atlas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-25 23:10:00</t>
+          <t>2026-09-26 03:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Liga MX - MEX AL</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Atlante vs Monterrey</t>
+          <t>Ceuta vs Real Sociedad II</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-26 01:00:00</t>
+          <t>2026-09-26 12:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -950,9 +950,17 @@
           <t>1.61</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
@@ -963,57 +971,57 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Primera Division - URY CL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Once Caldas vs Atlético Bucaramanga</t>
+          <t>Atlético Progreso vs Racing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-26 01:15:00</t>
+          <t>2026-09-26 14:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -1029,80 +1037,80 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Liga MX - MEX AL</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tijuana vs Atlas</t>
+          <t>Granada vs FC Andorra</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-26 03:00:00</t>
+          <t>2026-09-26 14:15:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -1116,17 +1124,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ceuta vs Real Sociedad II</t>
+          <t>Tenerife vs Cádiz</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-26 12:00:00</t>
+          <t>2026-09-26 16:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1136,45 +1144,37 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
@@ -1185,62 +1185,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Atlético Progreso vs Racing</t>
+          <t>Celta Fortuna vs Sabadell</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-26 14:00:00</t>
+          <t>2026-09-26 16:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
@@ -1251,139 +1259,123 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Primera Division - URY CL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Granada vs FC Andorra</t>
+          <t>Cerro Largo vs Nacional</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-09-26 14:15:00</t>
+          <t>2026-09-26 18:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>1.77</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
+      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tenerife vs Cádiz</t>
+          <t>Deportivo Pereira vs Internacional de Bogotá</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-09-26 16:30:00</t>
+          <t>2026-09-26 21:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1399,131 +1391,139 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Primera Division - URY CL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Celta Fortuna vs Sabadell</t>
+          <t>Peñarol vs Boston River</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-09-26 16:30:00</t>
+          <t>2026-09-26 21:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>Liga MX - MEX AL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cerro Largo vs Nacional</t>
+          <t>Cruz Azul vs Toluca</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-09-26 18:00:00</t>
+          <t>2026-09-26 22:50:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1539,57 +1539,57 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Liga MX - MEX AL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deportivo Pereira vs Internacional de Bogotá</t>
+          <t>Guadalajara vs Querétaro</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-09-26 21:00:00</t>
+          <t>2026-09-26 23:07:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -1605,145 +1605,137 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Peñarol vs Boston River</t>
+          <t>Cúcuta Deportivo vs Llaneros</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-09-26 21:30:00</t>
+          <t>2026-09-26 23:15:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
+      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Liga MX - MEX AL</t>
+          <t>Major League Soccer - USA MLS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cruz Azul vs Toluca</t>
+          <t>Philadelphia Union vs Orlando City</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-09-26 22:50:00</t>
+          <t>2026-09-26 23:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
@@ -1753,57 +1745,57 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Liga MX - MEX AL</t>
+          <t>Major League Soccer - USA MLS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Guadalajara vs Querétaro</t>
+          <t>Atlanta United vs New York City</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-09-26 23:07:00</t>
+          <t>2026-09-26 23:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1819,57 +1811,57 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Major League Soccer - USA MLS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cúcuta Deportivo vs Llaneros</t>
+          <t>CF Montréal vs Cincinnati</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-09-26 23:15:00</t>
+          <t>2026-09-26 23:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -1890,7 +1882,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Philadelphia Union vs Orlando City</t>
+          <t>Charlotte vs Chicago Fire</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1900,32 +1892,32 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1939,17 +1931,9 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
@@ -1964,7 +1948,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Atlanta United vs New York City</t>
+          <t>New York RB vs St. Louis City</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1974,42 +1958,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -2030,52 +2014,52 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CF Montréal vs Cincinnati</t>
+          <t>Dallas vs Los Angeles FC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-09-26 23:30:00</t>
+          <t>2026-09-27 00:30:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -2096,22 +2080,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Charlotte vs Chicago Fire</t>
+          <t>Seattle Sounders vs Minnesota United</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-09-26 23:30:00</t>
+          <t>2026-09-27 00:30:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2121,17 +2105,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2162,52 +2146,52 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>New York RB vs St. Louis City</t>
+          <t>Nashville SC vs Toronto</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-09-26 23:30:00</t>
+          <t>2026-09-27 00:30:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -2228,7 +2212,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Dallas vs Los Angeles FC</t>
+          <t>Austin vs San Diego</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2238,42 +2222,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -2294,7 +2278,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Seattle Sounders vs Minnesota United</t>
+          <t>Houston Dynamo vs Sporting KC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2304,30 +2288,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>4.59</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5.77</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
           <t>2.05</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -2343,12 +2339,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>Primera Division - URY CL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nashville SC vs Toronto</t>
+          <t>Montevideo City Torque vs Deportivo Maldonado</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2358,117 +2354,149 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
       <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Austin vs San Diego</t>
+          <t>Junior FC vs Independiente Medellín</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-09-27 00:30:00</t>
+          <t>2026-09-27 01:20:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
     </row>
@@ -2480,52 +2508,52 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Houston Dynamo vs Sporting KC</t>
+          <t>Real Salt Lake vs New England</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-09-27 00:30:00</t>
+          <t>2026-09-27 01:30:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2541,32 +2569,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>Major League Soccer - USA MLS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Montevideo City Torque vs Deportivo Maldonado</t>
+          <t>LA Galaxy vs Colorado Rapids</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-09-27 00:30:00</t>
+          <t>2026-09-27 02:30:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2576,130 +2604,114 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
+      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
+      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Major League Soccer - USA MLS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Junior FC vs Independiente Medellín</t>
+          <t>Vancouver Whitecaps vs DC United</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-09-27 01:20:00</t>
+          <t>2026-09-27 02:30:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
         <is>
           <t>1.83</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -2710,106 +2722,106 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Real Salt Lake vs New England</t>
+          <t>SJ Earthquakes vs Portland Timbers</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-09-27 01:30:00</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
+          <t>2026-09-27 02:30:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>3.87</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
       <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
       <c r="T33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>Liga MX - MEX AL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LA Galaxy vs Colorado Rapids</t>
+          <t>Santos Laguna vs Pachuca</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-09-27 02:30:00</t>
+          <t>2026-09-27 03:05:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>2.15</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -2825,47 +2837,47 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>Liga MX - MEX AL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps vs DC United</t>
+          <t>Tigres UANL vs Puebla</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-09-27 02:30:00</t>
+          <t>2026-09-27 03:10:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2879,173 +2891,217 @@
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+      <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>K League 1 - KOR KL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SJ Earthquakes vs Portland Timbers</t>
+          <t>Gangwon vs Incheon United</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-09-27 02:30:00</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>2026-09-27 10:00:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3.26</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
+      <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Liga MX - MEX AL</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Santos Laguna vs Pachuca</t>
+          <t>Real Valladolid vs Córdoba</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-09-27 03:05:00</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
+          <t>2026-09-27 12:00:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Liga MX - MEX AL</t>
+          <t>Primera Division - URY CL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tigres UANL vs Puebla</t>
+          <t>Central Español vs Liverpool</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-09-27 03:10:00</t>
+          <t>2026-09-27 14:00:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -3061,66 +3117,82 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>K League 1 - KOR KL</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gangwon vs Incheon United</t>
+          <t>Mallorca vs Almería</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-09-27 10:00:00</t>
+          <t>2026-09-27 14:15:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t>1.72</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
     </row>
@@ -3132,17 +3204,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Real Valladolid vs Córdoba</t>
+          <t>SD Eibar vs Las Palmas</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-09-27 12:00:00</t>
+          <t>2026-09-27 16:30:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3152,55 +3224,55 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="S40" t="inlineStr"/>
@@ -3209,62 +3281,70 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Central Español vs Liverpool</t>
+          <t>Burgos vs Eldense</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-09-27 14:00:00</t>
+          <t>2026-09-27 16:30:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
@@ -3275,17 +3355,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Liga MX - MEX AL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mallorca vs Almería</t>
+          <t>Pumas UNAM vs Atlético San Luis</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-09-27 14:15:00</t>
+          <t>2026-09-27 18:00:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3295,144 +3375,112 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
+      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Primera Division - URY CL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SD Eibar vs Las Palmas</t>
+          <t>Juventud vs Cerro</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-09-27 16:30:00</t>
+          <t>2026-09-27 18:00:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
+      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
+      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
     </row>
@@ -3444,17 +3492,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Burgos vs Eldense</t>
+          <t>Real Oviedo vs Sporting Gijón</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-09-27 16:30:00</t>
+          <t>2026-09-27 19:00:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3464,32 +3512,32 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -3505,57 +3553,57 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Liga MX - MEX AL</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Pumas UNAM vs Atlético San Luis</t>
+          <t>Jaguares de Córdoba vs Alianza Petrolera</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-09-27 18:00:00</t>
+          <t>2026-09-27 21:00:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -3576,52 +3624,52 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Juventud vs Cerro</t>
+          <t>Defensor Sporting vs Danubio</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-09-27 18:00:00</t>
+          <t>2026-09-27 21:00:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -3637,67 +3685,83 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Major League Soccer - USA MLS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Real Oviedo vs Sporting Gijón</t>
+          <t>Columbus Crew vs Inter Miami</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-09-27 19:00:00</t>
+          <t>2026-09-27 23:00:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
           <t>3.25</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>3.98</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
       <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
       <c r="T47" t="inlineStr"/>
     </row>
     <row r="48">
@@ -3708,52 +3772,52 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Jaguares de Córdoba vs Alianza Petrolera</t>
+          <t>Fortaleza CEIF vs Deportes Tolima</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-09-27 21:00:00</t>
+          <t>2026-09-27 23:05:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t>2.25</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -3769,57 +3833,57 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>Liga MX - MEX AL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Defensor Sporting vs Danubio</t>
+          <t>León vs Juárez</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-09-27 21:00:00</t>
+          <t>2026-09-28 01:00:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -3835,139 +3899,123 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Columbus Crew vs Inter Miami</t>
+          <t>Deportivo Cali vs Rionegro Águilas</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-09-27 23:00:00</t>
+          <t>2026-09-28 01:10:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
+      <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Liga MX - MEX AL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF vs Deportes Tolima</t>
+          <t>Necaxa vs América</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-09-27 23:05:00</t>
+          <t>2026-09-28 03:10:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -3980,6 +4028,196 @@
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>La Liga 2 - ESP S</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Leganés vs Castellón</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-09-28 18:30:00</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Primera Division - URY CL</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Wanderers vs Albion</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-09-28 23:00:00</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Liga BetPlay - COL PA</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Deportivo Pereira vs Santa Fe</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-09-29 20:30:00</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T2" r:id="rId1"/>

--- a/data/season_2026/next_games/next_games.xlsx
+++ b/data/season_2026/next_games/next_games.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:T27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,35 +504,25 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Pinnacle_Lines_Goals_Over_1.5</t>
+          <t>Pinnacle_Lines_Goals_Over_2.5</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Pinnacle_Lines_Goals_Over_2.5</t>
+          <t>Pinnacle_Lines_Goals_Over_3.5</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>Pinnacle_Lines_Goals_Over_3.5</t>
+          <t>Pinnacle_Lines_Goals_Under_2.5</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>Pinnacle_Lines_Goals_Under_1.5</t>
+          <t>Pinnacle_Lines_Goals_Under_3.5</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
-        <is>
-          <t>Pinnacle_Lines_Goals_Under_2.5</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Pinnacle_Lines_Goals_Under_3.5</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
         <is>
           <t>Para mais mercados visite o site</t>
         </is>
@@ -541,86 +531,92 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Real Oviedo vs Sporting Gijón</t>
+          <t>Deportivo Pereira vs Santa Fe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-27 19:00:00</t>
+          <t>2026-09-29 20:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>4.56</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" s="1" t="inlineStr">
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t>https://www.quantumodds.xyz/</t>
         </is>
@@ -634,65 +630,79 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jaguares de Córdoba vs Alianza Petrolera</t>
+          <t>Independiente Medellín vs Millonarios</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-27 21:00:00</t>
+          <t>2026-09-30 01:05:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -702,42 +712,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Defensor Sporting vs Danubio</t>
+          <t>Montevideo City Torque vs Peñarol</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-27 21:00:00</t>
+          <t>2026-09-30 23:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -750,17 +760,23 @@
           <t>1.83</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -770,42 +786,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Columbus Crew vs Inter Miami</t>
+          <t>New York RB vs St. Louis City</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-27 23:00:00</t>
+          <t>2026-09-30 23:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -819,32 +835,14 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>2.04</t>
-        </is>
-      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -854,52 +852,52 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF vs Deportes Tolima</t>
+          <t>Atlético Nacional vs Junior FC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-27 23:05:00</t>
+          <t>2026-10-01 01:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>6.70</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -911,199 +909,217 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Liga MX - MEX AL</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>León vs Juárez</t>
+          <t>Internacional de Bogotá vs Once Caldas</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-28 01:00:00</t>
+          <t>2026-10-02 01:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Major League Soccer - USA MLS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deportivo Cali vs Rionegro Águilas</t>
+          <t>Seattle Sounders vs Sporting KC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-28 01:10:00</t>
+          <t>2026-10-02 01:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
       <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Liga MX - MEX AL</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Necaxa vs América</t>
+          <t>Eldense vs Real Oviedo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-28 03:10:00</t>
+          <t>2026-10-02 18:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -1115,524 +1131,1326 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Leganés vs Castellón</t>
+          <t>Independiente vs Instituto</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-28 18:30:00</t>
+          <t>2026-10-02 22:15:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wanderers vs Albion</t>
+          <t>São Paulo vs Santos</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-28 23:00:00</t>
+          <t>2026-10-02 23:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deportivo Pereira vs Santa Fe</t>
+          <t>Independiente Rivadavia vs Gimnasia La Plata</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:00</t>
+          <t>2026-10-03 00:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>1.80</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Independiente Medellín vs Millonarios</t>
+          <t>Boca Juniors vs Unión Santa Fe</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-09-30 01:05:00</t>
+          <t>2026-10-03 00:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Montevideo City Torque vs Peñarol</t>
+          <t>Deportivo Cali vs Alianza Petrolera</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-09-30 23:00:00</t>
+          <t>2026-10-03 00:45:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>New York RB vs St. Louis City</t>
+          <t>Albacete vs SD Eibar</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-09-30 23:30:00</t>
+          <t>2026-10-03 12:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Primera Division - URY CL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Atlético Nacional vs Junior FC</t>
+          <t>Liverpool vs Atlético Progreso</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-01 01:00:00</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+          <t>2026-10-03 14:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6.96</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+          <t>4.79</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>La Liga 2 - ESP S</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Almería vs Burgos</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-10-03 14:15:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>3.92</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5.43</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>La Liga 2 - ESP S</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Sabadell vs FC Andorra</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-10-03 16:30:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3.89</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>La Liga 2 - ESP S</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Cádiz vs Leganés</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-10-03 16:30:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Defensa y Justicia vs San Lorenzo</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-10-03 17:45:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4.18</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Primera Division - URY CL</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Albion vs Defensor Sporting</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-10-03 18:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2.84</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Liga BetPlay - COL PA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Rionegro Águilas vs Jaguares de Córdoba</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-10-03 19:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>3.87</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5.83</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Atlético Tucumán vs Barracas Central</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-10-03 20:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4.70</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Newell's Old Boys vs Lanús</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-10-03 20:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2.84</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Primera Division - URY CL</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Deportivo Maldonado vs Central Español</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-10-03 21:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>3.77</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5.24</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Liga BetPlay - COL PA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Deportes Tolima vs Boyacá Chicó</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-10-03 21:05:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>4.79</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10.46</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Serie A - BRA CB</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro vs Bragantino</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-10-03 21:30:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/season_2026/next_games/next_games.xlsx
+++ b/data/season_2026/next_games/next_games.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T27"/>
+  <dimension ref="A1:V45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,45 +484,55 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>Bet365_Lines_Goals_Over_1.5</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>Bet365_Lines_Goals_Over_2.5</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Bet365_Lines_Goals_Over_3.5</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Bet365_Lines_Goals_Under_1.5</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
         <is>
           <t>Bet365_Lines_Goals_Under_2.5</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Bet365_Lines_Goals_Under_3.5</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Pinnacle_Lines_Goals_Over_2.5</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Pinnacle_Lines_Goals_Over_3.5</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Pinnacle_Lines_Goals_Under_2.5</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Pinnacle_Lines_Goals_Under_3.5</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Para mais mercados visite o site</t>
         </is>
@@ -536,87 +546,81 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Deportivo Pereira vs Santa Fe</t>
+          <t>Internacional de Bogotá vs Once Caldas</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:00</t>
+          <t>2026-10-02 01:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>2.00</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="T2" s="1" t="inlineStr">
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" s="1" t="inlineStr">
         <is>
           <t>https://www.quantumodds.xyz/</t>
         </is>
@@ -625,213 +629,209 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Major League Soccer - USA MLS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Independiente Medellín vs Millonarios</t>
+          <t>Seattle Sounders vs Sporting KC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-30 01:05:00</t>
+          <t>2026-10-02 01:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>1.86</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Montevideo City Torque vs Peñarol</t>
+          <t>Eldense vs Real Oviedo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-30 23:00:00</t>
+          <t>2026-10-02 18:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>2.91</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2.41</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>New York RB vs St. Louis City</t>
+          <t>Independiente vs Instituto</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-30 23:30:00</t>
+          <t>2026-10-02 22:15:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -843,61 +843,63 @@
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Atlético Nacional vs Junior FC</t>
+          <t>São Paulo vs Santos</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-01 01:00:00</t>
+          <t>2026-10-02 23:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.70</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -909,217 +911,215 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá vs Once Caldas</t>
+          <t>Independiente Rivadavia vs Gimnasia La Plata</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-02 01:00:00</t>
+          <t>2026-10-03 00:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Seattle Sounders vs Sporting KC</t>
+          <t>Boca Juniors vs Unión Santa Fe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-02 01:30:00</t>
+          <t>2026-10-03 00:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Eldense vs Real Oviedo</t>
+          <t>Deportivo Cali vs Alianza Petrolera</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-02 18:30:00</t>
+          <t>2026-10-03 00:45:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -1131,275 +1131,315 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Independiente vs Instituto</t>
+          <t>Albacete vs SD Eibar</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-02 22:15:00</t>
+          <t>2026-10-03 12:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
       <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>Primera Division - URY CL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>São Paulo vs Santos</t>
+          <t>Liverpool vs Atlético Progreso</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:00</t>
+          <t>2026-10-03 14:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia vs Gimnasia La Plata</t>
+          <t>Almería vs Burgos</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-03 00:30:00</t>
+          <t>2026-10-03 14:15:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
           <t>1.95</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Boca Juniors vs Unión Santa Fe</t>
+          <t>Sabadell vs FC Andorra</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-03 00:30:00</t>
+          <t>2026-10-03 16:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>3.60</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1411,61 +1451,63 @@
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deportivo Cali vs Alianza Petrolera</t>
+          <t>Cádiz vs Leganés</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-03 00:45:00</t>
+          <t>2026-10-03 16:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -1477,88 +1519,76 @@
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Albacete vs SD Eibar</t>
+          <t>Defensa y Justicia vs San Lorenzo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:00</t>
+          <t>2026-10-03 17:45:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1568,42 +1598,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Liverpool vs Atlético Progreso</t>
+          <t>Albion vs Defensor Sporting</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-03 14:00:00</t>
+          <t>2026-10-03 18:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1616,76 +1646,70 @@
           <t>1.83</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
+      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Almería vs Burgos</t>
+          <t>Rionegro Águilas vs Jaguares de Córdoba</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-03 14:15:00</t>
+          <t>2026-10-03 19:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1698,86 +1722,88 @@
           <t>1.90</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sabadell vs FC Andorra</t>
+          <t>Atlético Tucumán vs Barracas Central</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-03 16:30:00</t>
+          <t>2026-10-03 20:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1789,61 +1815,63 @@
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cádiz vs Leganés</t>
+          <t>Newell's Old Boys vs Lanús</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-03 16:30:00</t>
+          <t>2026-10-03 20:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>2.75</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1855,334 +1883,384 @@
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>Primera Division - URY CL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Defensa y Justicia vs San Lorenzo</t>
+          <t>Deportivo Maldonado vs Central Español</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-03 17:45:00</t>
+          <t>2026-10-03 21:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
       <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Albion vs Defensor Sporting</t>
+          <t>Deportes Tolima vs Boyacá Chicó</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-03 18:00:00</t>
+          <t>2026-10-03 21:05:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>10.46</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
       <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rionegro Águilas vs Jaguares de Córdoba</t>
+          <t>Atlético Mineiro vs Bragantino</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-03 19:00:00</t>
+          <t>2026-10-03 21:30:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>Liga Portugal 2 - PRT SL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Atlético Tucumán vs Barracas Central</t>
+          <t>Farense vs Chaves</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:00</t>
+          <t>2026-10-04 10:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
           <t>1.95</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4.70</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2.37</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
       <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Newell's Old Boys vs Lanús</t>
+          <t>Real Sociedad II vs Granada</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:00</t>
+          <t>2026-10-04 12:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2192,23 +2270,41 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
       <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2218,221 +2314,197 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado vs Central Español</t>
+          <t>Danubio vs Cerro Largo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-03 21:00:00</t>
+          <t>2026-10-04 13:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
+      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
+      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Deportes Tolima vs Boyacá Chicó</t>
+          <t>Sporting Gijón vs Celta Fortuna</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-03 21:05:00</t>
+          <t>2026-10-04 14:15:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10.46</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
+      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>Primera Division - URY CL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Atlético Mineiro vs Bragantino</t>
+          <t>Boston River vs Juventud</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-03 21:30:00</t>
+          <t>2026-10-04 16:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
           <t>2.10</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -2442,15 +2514,1317 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>La Liga 2 - ESP S</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Las Palmas vs Real Valladolid</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-10-04 16:30:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>La Liga 2 - ESP S</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Castellón vs Ceuta</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-10-04 16:30:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>6.32</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>9.62</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Huracán vs Aldosivi</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-10-04 17:45:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5.58</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Liga BetPlay - COL PA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto vs Fortaleza CEIF</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-10-04 19:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>La Liga 2 - ESP S</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Girona vs Mallorca</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-10-04 19:00:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Primera Division - URY CL</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Cerro vs Wanderers</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-10-04 19:00:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Talleres Córdoba vs Belgrano</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-10-04 20:00:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Liga BetPlay - COL PA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Cúcuta Deportivo vs Deportivo Pereira</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-10-04 21:05:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>3.49</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>4.72</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors vs Tigre</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-10-04 22:15:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>4.84</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Primera Division - URY CL</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Racing vs Peñarol</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-10-04 22:30:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Liga BetPlay - COL PA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Junior FC</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-10-04 23:10:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Estudiantes de Río Cuarto vs Racing Club</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-10-05 00:30:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Liga BetPlay - COL PA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Llaneros vs América de Cali</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:15:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>3.53</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>La Liga 2 - ESP S</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Córdoba vs Tenerife</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-10-05 18:30:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>3.59</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3.93</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Deportivo Riestra vs Central Cordoba SdE</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-10-05 19:45:00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4.87</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Vélez Sarsfield vs Platense</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:00:00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4.63</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Estudiantes vs Gimnasia y Esgrima Mendoza</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:00:00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5.08</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Primera Division - URY CL</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Nacional vs Montevideo City Torque</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-10-05 23:00:00</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/season_2026/next_games/next_games.xlsx
+++ b/data/season_2026/next_games/next_games.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V45"/>
+  <dimension ref="A1:X39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,25 +514,35 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>Pinnacle_Lines_Goals_Over_1.5</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>Pinnacle_Lines_Goals_Over_2.5</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Pinnacle_Lines_Goals_Over_3.5</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Pinnacle_Lines_Goals_Under_1.5</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
         <is>
           <t>Pinnacle_Lines_Goals_Under_2.5</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Pinnacle_Lines_Goals_Under_3.5</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Para mais mercados visite o site</t>
         </is>
@@ -546,81 +556,83 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá vs Once Caldas</t>
+          <t>Rionegro Águilas vs Jaguares de Córdoba</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-02 01:00:00</t>
+          <t>2026-10-03 19:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2.04</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" s="1" t="inlineStr">
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" s="1" t="inlineStr">
         <is>
           <t>https://www.quantumodds.xyz/</t>
         </is>
@@ -629,131 +641,125 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Seattle Sounders vs Sporting KC</t>
+          <t>Atlético Tucumán vs Barracas Central</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-02 01:30:00</t>
+          <t>2026-10-03 20:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>2.62</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>1.44</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Eldense vs Real Oviedo</t>
+          <t>Newell's Old Boys vs Lanús</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-02 18:30:00</t>
+          <t>2026-10-03 20:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -772,619 +778,677 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
       <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>Primera Division - URY CL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Independiente vs Instituto</t>
+          <t>Deportivo Maldonado vs Central Español</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-02 22:15:00</t>
+          <t>2026-10-03 21:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>São Paulo vs Santos</t>
+          <t>Deportes Tolima vs Boyacá Chicó</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:00</t>
+          <t>2026-10-03 21:05:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia vs Gimnasia La Plata</t>
+          <t>Atlético Mineiro vs Bragantino</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-03 00:30:00</t>
+          <t>2026-10-03 21:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>3.51</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4.36</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>1.86</t>
-        </is>
-      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>Liga Portugal 2 - PRT SL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Boca Juniors vs Unión Santa Fe</t>
+          <t>Farense vs Chaves</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-03 00:30:00</t>
+          <t>2026-10-04 10:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Deportivo Cali vs Alianza Petrolera</t>
+          <t>Real Sociedad II vs Granada</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-03 00:45:00</t>
+          <t>2026-10-04 12:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Primera Division - URY CL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Albacete vs SD Eibar</t>
+          <t>Danubio vs Cerro Largo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-03 12:00:00</t>
+          <t>2026-10-04 13:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Liverpool vs Atlético Progreso</t>
+          <t>Sporting Gijón vs Celta Fortuna</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-03 14:00:00</t>
+          <t>2026-10-04 14:15:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Primera Division - URY CL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Almería vs Burgos</t>
+          <t>Boston River vs Juventud</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-03 14:15:00</t>
+          <t>2026-10-04 16:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1394,52 +1458,52 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sabadell vs FC Andorra</t>
+          <t>Las Palmas vs Real Valladolid</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-03 16:30:00</t>
+          <t>2026-10-04 16:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1449,10 +1513,20 @@
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1462,65 +1536,83 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cádiz vs Leganés</t>
+          <t>Castellón vs Ceuta</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-03 16:30:00</t>
+          <t>2026-10-04 16:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>11.00</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>11.55</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>1.80</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>1.90</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1530,52 +1622,52 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Defensa y Justicia vs San Lorenzo</t>
+          <t>Huracán vs Aldosivi</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-03 17:45:00</t>
+          <t>2026-10-04 17:45:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1589,51 +1681,53 @@
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Albion vs Defensor Sporting</t>
+          <t>Deportivo Pasto vs Fortaleza CEIF</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-03 18:00:00</t>
+          <t>2026-10-04 19:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1647,163 +1741,159 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rionegro Águilas vs Jaguares de Córdoba</t>
+          <t>Girona vs Mallorca</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-03 19:00:00</t>
+          <t>2026-10-04 19:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>Primera Division - URY CL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Atlético Tucumán vs Barracas Central</t>
+          <t>Cerro vs Wanderers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:00</t>
+          <t>2026-10-04 19:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1817,6 +1907,8 @@
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1826,58 +1918,66 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Newell's Old Boys vs Lanús</t>
+          <t>Talleres Córdoba vs Belgrano</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:00</t>
+          <t>2026-10-04 20:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
@@ -1885,90 +1985,94 @@
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado vs Central Español</t>
+          <t>Internacional de Bogotá vs Once Caldas</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-03 21:00:00</t>
+          <t>2026-10-04 21:05:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>1.80</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>1.90</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr">
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
         <is>
           <t>1.80</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1978,353 +2082,321 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deportes Tolima vs Boyacá Chicó</t>
+          <t>Cúcuta Deportivo vs Deportivo Pereira</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-03 21:05:00</t>
+          <t>2026-10-04 21:05:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10.46</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Atlético Mineiro vs Bragantino</t>
+          <t>Argentinos Juniors vs Tigre</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-03 21:30:00</t>
+          <t>2026-10-04 22:15:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
+      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
+      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Liga Portugal 2 - PRT SL</t>
+          <t>Primera Division - URY CL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Farense vs Chaves</t>
+          <t>Racing vs Peñarol</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-04 10:00:00</t>
+          <t>2026-10-04 22:30:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>2.10</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>3.32</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
+      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
+      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Real Sociedad II vs Granada</t>
+          <t>Atlético Bucaramanga vs Junior FC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-04 12:00:00</t>
+          <t>2026-10-04 23:10:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
+      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Danubio vs Cerro Largo</t>
+          <t>Estudiantes de Río Cuarto vs Racing Club</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-04 13:00:00</t>
+          <t>2026-10-05 00:30:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2334,32 +2406,32 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -2373,61 +2445,63 @@
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sporting Gijón vs Celta Fortuna</t>
+          <t>Llaneros vs América de Cali</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-04 14:15:00</t>
+          <t>2026-10-05 01:15:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -2441,145 +2515,149 @@
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Boston River vs Juventud</t>
+          <t>Córdoba vs Tenerife</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-04 16:00:00</t>
+          <t>2026-10-05 18:30:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>1.79</t>
-        </is>
-      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Las Palmas vs Real Valladolid</t>
+          <t>Deportivo Riestra vs Central Cordoba SdE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-04 16:30:00</t>
+          <t>2026-10-05 19:45:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -2588,103 +2666,83 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>2.06</t>
-        </is>
-      </c>
+      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Castellón vs Ceuta</t>
+          <t>Vélez Sarsfield vs Platense</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-04 16:30:00</t>
+          <t>2026-10-05 22:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>9.62</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
+      <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2694,17 +2752,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Huracán vs Aldosivi</t>
+          <t>Estudiantes vs Gimnasia y Esgrima Mendoza</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-04 17:45:00</t>
+          <t>2026-10-05 22:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2714,32 +2772,32 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5.08</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
           <t>1.70</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5.58</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2753,208 +2811,230 @@
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Primera Division - URY CL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Deportivo Pasto vs Fortaleza CEIF</t>
+          <t>Nacional vs Montevideo City Torque</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-04 19:00:00</t>
+          <t>2026-10-05 23:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
           <t>3.27</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3.82</t>
-        </is>
-      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Girona vs Mallorca</t>
+          <t>Independiente Medellín vs Santa Fe</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-04 19:00:00</t>
+          <t>2026-10-06 00:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cerro vs Wanderers</t>
+          <t>Banfield vs Rosario Central</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-04 19:00:00</t>
+          <t>2026-10-06 00:15:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2973,75 +3053,69 @@
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>Major League Soccer - USA MLS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Talleres Córdoba vs Belgrano</t>
+          <t>Chicago Fire vs Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-04 20:00:00</t>
+          <t>2026-10-07 00:30:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>1.77</t>
-        </is>
-      </c>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
@@ -3049,110 +3123,114 @@
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cúcuta Deportivo vs Deportivo Pereira</t>
+          <t>Remo vs Grêmio</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-04 21:05:00</t>
+          <t>2026-10-07 22:30:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
           <t>3.50</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>3.49</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Argentinos Juniors vs Tigre</t>
+          <t>Internacional vs Corinthians</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-04 22:15:00</t>
+          <t>2026-10-07 22:30:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3162,32 +3240,32 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -3201,21 +3279,23 @@
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Racing vs Peñarol</t>
+          <t>Bragantino vs Mirassol</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-04 22:30:00</t>
+          <t>2026-10-07 22:30:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -3237,594 +3317,184 @@
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga vs Junior FC</t>
+          <t>Vitória vs Chapecoense</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-04 23:10:00</t>
+          <t>2026-10-07 23:00:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>1.79</t>
-        </is>
-      </c>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Estudiantes de Río Cuarto vs Racing Club</t>
+          <t>Botafogo vs Vasco da Gama</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-05 00:30:00</t>
+          <t>2026-10-07 23:30:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Liga BetPlay - COL PA</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Llaneros vs América de Cali</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2026-10-05 01:15:00</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>3.53</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>3.14</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>La Liga 2 - ESP S</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Córdoba vs Tenerife</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2026-10-05 18:30:00</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>3.59</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>3.93</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Deportivo Riestra vs Central Cordoba SdE</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2026-10-05 19:45:00</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>3.08</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>4.87</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Vélez Sarsfield vs Platense</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2026-10-05 22:00:00</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>4.63</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Estudiantes vs Gimnasia y Esgrima Mendoza</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2026-10-05 22:00:00</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>3.62</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5.08</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Primera Division - URY CL</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Nacional vs Montevideo City Torque</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2026-10-05 23:00:00</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>3.67</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/season_2026/next_games/next_games.xlsx
+++ b/data/season_2026/next_games/next_games.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X39"/>
+  <dimension ref="A1:T47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,65 +484,45 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Bet365_Lines_Goals_Over_1.5</t>
+          <t>Bet365_Lines_Goals_Over_2.5</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Bet365_Lines_Goals_Over_2.5</t>
+          <t>Bet365_Lines_Goals_Over_3.5</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Bet365_Lines_Goals_Over_3.5</t>
+          <t>Bet365_Lines_Goals_Under_2.5</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Bet365_Lines_Goals_Under_1.5</t>
+          <t>Bet365_Lines_Goals_Under_3.5</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Bet365_Lines_Goals_Under_2.5</t>
+          <t>Pinnacle_Lines_Goals_Over_2.5</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Bet365_Lines_Goals_Under_3.5</t>
+          <t>Pinnacle_Lines_Goals_Over_3.5</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>Pinnacle_Lines_Goals_Over_1.5</t>
+          <t>Pinnacle_Lines_Goals_Under_2.5</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>Pinnacle_Lines_Goals_Over_2.5</t>
+          <t>Pinnacle_Lines_Goals_Under_3.5</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
-        <is>
-          <t>Pinnacle_Lines_Goals_Over_3.5</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Pinnacle_Lines_Goals_Under_1.5</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Pinnacle_Lines_Goals_Under_2.5</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Pinnacle_Lines_Goals_Under_3.5</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
         <is>
           <t>Para mais mercados visite o site</t>
         </is>
@@ -551,88 +531,76 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rionegro Águilas vs Jaguares de Córdoba</t>
+          <t>Deportivo Riestra vs Central Cordoba SdE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-03 19:00:00</t>
+          <t>2026-10-05 19:45:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" s="1" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t>https://www.quantumodds.xyz/</t>
         </is>
@@ -646,52 +614,52 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Atlético Tucumán vs Barracas Central</t>
+          <t>Vélez Sarsfield vs Platense</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:00</t>
+          <t>2026-10-05 22:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -700,21 +668,9 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -724,52 +680,52 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Newell's Old Boys vs Lanús</t>
+          <t>Estudiantes vs Gimnasia y Esgrima Mendoza</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:00</t>
+          <t>2026-10-05 22:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -778,21 +734,9 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -802,83 +746,79 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado vs Central Español</t>
+          <t>Nacional vs Montevideo City Torque</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-03 21:00:00</t>
+          <t>2026-10-05 23:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -888,396 +828,348 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deportes Tolima vs Boyacá Chicó</t>
+          <t>Independiente Medellín vs Santa Fe</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-03 21:05:00</t>
+          <t>2026-10-06 00:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2.37</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>1.86</t>
-        </is>
-      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Atlético Mineiro vs Bragantino</t>
+          <t>Banfield vs Rosario Central</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-03 21:30:00</t>
+          <t>2026-10-06 00:15:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4.36</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>3.40</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2.14</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>3.54</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>2.04</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Liga Portugal 2 - PRT SL</t>
+          <t>Major League Soccer - USA MLS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Farense vs Chaves</t>
+          <t>Chicago Fire vs Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-04 10:00:00</t>
+          <t>2026-10-07 00:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>1.86</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Real Sociedad II vs Granada</t>
+          <t>Remo vs Grêmio</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-04 12:00:00</t>
+          <t>2026-10-07 22:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Danubio vs Cerro Largo</t>
+          <t>Internacional vs Corinthians</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-04 13:00:00</t>
+          <t>2026-10-07 22:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>1.90</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>3.19</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3.82</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -1289,294 +1181,302 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sporting Gijón vs Celta Fortuna</t>
+          <t>Bragantino vs Mirassol</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-04 14:15:00</t>
+          <t>2026-10-07 22:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Boston River vs Juventud</t>
+          <t>Vitória vs Chapecoense</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-04 16:00:00</t>
+          <t>2026-10-07 23:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>1.95</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
+      <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Las Palmas vs Real Valladolid</t>
+          <t>Botafogo vs Vasco da Gama</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-04 16:30:00</t>
+          <t>2026-10-07 23:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>2.20</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2.26</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>3.35</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3.36</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>2.06</t>
-        </is>
-      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Castellón vs Ceuta</t>
+          <t>Cruzeiro vs São Paulo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-04 16:30:00</t>
+          <t>2026-10-08 00:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>11.55</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1584,316 +1484,324 @@
           <t>1.80</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Huracán vs Aldosivi</t>
+          <t>Atlético Nacional vs Deportes Tolima</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-04 17:45:00</t>
+          <t>2026-10-08 01:20:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2.37</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deportivo Pasto vs Fortaleza CEIF</t>
+          <t>Santos vs Flamengo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-04 19:00:00</t>
+          <t>2026-10-08 22:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Girona vs Mallorca</t>
+          <t>Athletico PR vs Atlético Mineiro</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-04 19:00:00</t>
+          <t>2026-10-08 23:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>1.86</t>
-        </is>
-      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cerro vs Wanderers</t>
+          <t>Palmeiras vs Bahia</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-04 19:00:00</t>
+          <t>2026-10-09 00:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1905,55 +1813,51 @@
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Talleres Córdoba vs Belgrano</t>
+          <t>Fluminense vs Coritiba</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-04 20:00:00</t>
+          <t>2026-10-09 00:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1968,25 +1872,29 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1996,224 +1904,192 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá vs Once Caldas</t>
+          <t>Fortaleza CEIF vs Millonarios</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-04 21:05:00</t>
+          <t>2026-10-09 01:10:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>1.90</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
           <t>1.82</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
+      <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>K League 1 - KOR KL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cúcuta Deportivo vs Deportivo Pereira</t>
+          <t>Daejeon Citizen vs Jeonbuk Motors</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-04 21:05:00</t>
+          <t>2026-10-09 05:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
+      <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>K League 1 - KOR KL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Argentinos Juniors vs Tigre</t>
+          <t>Incheon United vs Pohang Steelers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-04 22:15:00</t>
+          <t>2026-10-09 07:30:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>3.20</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -2225,65 +2101,61 @@
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>K League 1 - KOR KL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Racing vs Peñarol</t>
+          <t>Gangwon vs Bucheon 1995</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-04 22:30:00</t>
+          <t>2026-10-09 07:30:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>3.50</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3.59</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4.72</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>2.00</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>4.11</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2.91</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2.10</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -2295,143 +2167,143 @@
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>J1 League - JPN JL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga vs Junior FC</t>
+          <t>Kashiwa Reysol vs Vissel Kobe</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-04 23:10:00</t>
+          <t>2026-10-09 10:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
           <t>1.95</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>3.35</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3.92</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>2.04</t>
-        </is>
-      </c>
+      <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>J1 League - JPN JL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Estudiantes de Río Cuarto vs Racing Club</t>
+          <t>Kashima Antlers vs Gamba Osaka</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-05 00:30:00</t>
+          <t>2026-10-09 10:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -2443,67 +2315,43 @@
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Pro League - SAU PL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Llaneros vs América de Cali</t>
+          <t>Al Kholood vs Al-Qadsiah</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-05 01:15:00</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
+          <t>2026-10-09 13:50:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -2513,221 +2361,169 @@
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Pro League - SAU PL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Córdoba vs Tenerife</t>
+          <t>Al Fateh vs Al Ahli</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-05 18:30:00</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
+          <t>2026-10-09 14:55:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3.93</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>Premier League - None</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Deportivo Riestra vs Central Cordoba SdE</t>
+          <t>Rostov vs Akron</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-05 19:45:00</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
+          <t>2026-10-09 16:30:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4.87</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
+          <t>4.32</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
       <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>2. Bundesliga - GER BII</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield vs Platense</t>
+          <t>Eintracht Braunschweig vs Holstein Kiel</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-05 22:00:00</t>
+          <t>2026-10-09 16:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>1.44</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>2.62</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -2739,65 +2535,61 @@
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>2. Bundesliga - GER BII</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Estudiantes vs Gimnasia y Esgrima Mendoza</t>
+          <t>FC Heidenheim vs Kaiserslautern</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-05 22:00:00</t>
+          <t>2026-10-09 16:30:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2809,237 +2601,181 @@
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>Superliga - DNK SL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nacional vs Montevideo City Torque</t>
+          <t>Nordsjælland vs Odense BK</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-05 23:00:00</t>
+          <t>2026-10-09 17:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Liga Portugal 2 - PRT SL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Independiente Medellín vs Santa Fe</t>
+          <t>Penafiel vs AVS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
+          <t>2026-10-09 17:00:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4.04</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
+          <t>4.39</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
+      <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>Super Lig - TUR SL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Banfield vs Rosario Central</t>
+          <t>Galatasaray vs Kasımpaşa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-06 00:15:00</t>
+          <t>2026-10-09 17:00:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>11.00</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -3051,65 +2787,61 @@
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Chicago Fire vs Vancouver Whitecaps</t>
+          <t>Aldosivi vs Sarmiento</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-07 00:30:00</t>
+          <t>2026-10-09 17:30:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -3121,30 +2853,26 @@
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>Liga Portugal - PRT PL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Remo vs Grêmio</t>
+          <t>Moreirense vs Gil Vicente</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-07 22:30:00</t>
+          <t>2026-10-09 17:45:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3154,118 +2882,98 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
           <t>2.25</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>3.13</t>
-        </is>
-      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
+      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+      <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>Eredivisie - NLD E</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Internacional vs Corinthians</t>
+          <t>PSV vs SC Heerenveen</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-07 22:30:00</t>
+          <t>2026-10-09 18:00:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>8.17</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -3277,33 +2985,41 @@
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>Pro League - SAU PL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bragantino vs Mirassol</t>
+          <t>Al Nassr vs Al Diraiyah FC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-07 22:30:00</t>
+          <t>2026-10-09 18:00:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>5.09</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>5.28</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
@@ -3311,85 +3027,93 @@
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
       <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
       <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>Bundesliga - GER BI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vitória vs Chapecoense</t>
+          <t>Borussia Dortmund vs Werder Bremen</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-07 23:00:00</t>
+          <t>2026-10-09 18:30:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
@@ -3397,104 +3121,596 @@
         </is>
       </c>
       <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>Ligue 1 - FRA L1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Botafogo vs Vasco da Gama</t>
+          <t>Lens vs Olympique Lyonnais</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-07 23:30:00</t>
+          <t>2026-10-09 18:45:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t>2.70</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
+      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
+      <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Pro League - BEL FDA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SK Beveren vs Lommel SK</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-10-09 18:45:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>3.94</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>La Liga - ESP PL</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Málaga vs Espanyol</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-10-09 19:00:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Liga Portugal - PRT PL</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Sporting Braga vs Sporting CP</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-10-09 19:15:00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>3.52</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Primera Division - URY CL</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Montevideo City Torque vs Danubio</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-10-09 20:00:00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Gimnasia La Plata vs Atlético Tucumán</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-10-09 21:00:00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Instituto vs Boca Juniors</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-10-09 22:30:00</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Liga BetPlay - COL PA</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Alianza Petrolera vs Rionegro Águilas</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-10-09 23:00:00</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Primera Division - URY CL</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Deportivo Maldonado vs Liverpool</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-10-09 23:00:00</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/season_2026/next_games/next_games.xlsx
+++ b/data/season_2026/next_games/next_games.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V66"/>
+  <dimension ref="A1:T119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,35 +504,25 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Pinnacle_Lines_Goals_Over_1.5</t>
+          <t>Pinnacle_Lines_Goals_Over_2.5</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Pinnacle_Lines_Goals_Over_2.5</t>
+          <t>Pinnacle_Lines_Goals_Over_3.5</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>Pinnacle_Lines_Goals_Over_3.5</t>
+          <t>Pinnacle_Lines_Goals_Under_2.5</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>Pinnacle_Lines_Goals_Under_1.5</t>
+          <t>Pinnacle_Lines_Goals_Under_3.5</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
-        <is>
-          <t>Pinnacle_Lines_Goals_Under_2.5</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Pinnacle_Lines_Goals_Under_3.5</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
         <is>
           <t>Para mais mercados visite o site</t>
         </is>
@@ -541,86 +531,84 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Serie A - ITA SA</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cagliari vs Juventus</t>
+          <t>Atlético Bucaramanga vs Rionegro Águilas</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-11 18:45:00</t>
+          <t>2026-10-13 23:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
       <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>1.86</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" s="1" t="inlineStr">
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t>https://www.quantumodds.xyz/</t>
         </is>
@@ -629,217 +617,205 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ligue 1 - FRA L1</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Troyes vs Olympique Marseille</t>
+          <t>Millonarios vs Once Caldas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-11 18:45:00</t>
+          <t>2026-10-14 01:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
       <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Atlético Mineiro vs Santos</t>
+          <t>Junior FC vs Deportivo Pereira</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-11 19:00:00</t>
+          <t>2026-10-14 21:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>La Liga - ESP PL</t>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Racing Santander vs Valencia</t>
+          <t>Sarmiento vs River Plate</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-11 19:00:00</t>
+          <t>2026-10-14 22:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -851,755 +827,727 @@
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Major League Soccer - USA MLS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cádiz vs Sporting Gijón</t>
+          <t>Inter Miami vs New York City</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-11 19:00:00</t>
+          <t>2026-10-14 23:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Liga Portugal - PRT PL</t>
+          <t>Major League Soccer - USA MLS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Arouca vs Estrela Amadora</t>
+          <t>Columbus Crew vs Charlotte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-11 19:30:00</t>
+          <t>2026-10-14 23:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>Major League Soccer - USA MLS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rosario Central vs Independiente Rivadavia</t>
+          <t>Cincinnati vs New England</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-11 20:00:00</t>
+          <t>2026-10-14 23:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
       <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>Major League Soccer - USA MLS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Platense vs Argentinos Juniors</t>
+          <t>Toronto vs Orlando City</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-11 20:00:00</t>
+          <t>2026-10-14 23:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3.78</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>2.75</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>3.35</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2.89</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>Major League Soccer - USA MLS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Grêmio vs Internacional</t>
+          <t>CF Montréal vs Atlanta United</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-11 20:30:00</t>
+          <t>2026-10-14 23:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>Major League Soccer - USA MLS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Palmeiras vs Corinthians</t>
+          <t>DC United vs New York RB</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-11 20:30:00</t>
+          <t>2026-10-14 23:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>3.50</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Flamengo vs Fluminense</t>
+          <t>Santa Fe vs Jaguares de Córdoba</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-11 20:30:00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+          <t>2026-10-14 23:30:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4.86</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>9.61</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Major League Soccer - USA MLS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jaguares de Córdoba vs Deportes Tolima</t>
+          <t>Dallas vs Seattle Sounders</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-11 21:05:00</t>
+          <t>2026-10-15 00:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>3.75</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>5.13</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>Major League Soccer - USA MLS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Central Español vs Nacional</t>
+          <t>Chicago Fire vs Philadelphia Union</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:00</t>
+          <t>2026-10-15 00:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>3.70</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>5.81</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>3.85</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>Major League Soccer - USA MLS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Racing Club vs Belgrano</t>
+          <t>St. Louis City vs Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-11 22:15:00</t>
+          <t>2026-10-15 00:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1611,76 +1559,88 @@
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>Major League Soccer - USA MLS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bahia vs Mirassol</t>
+          <t>Nashville SC vs Sporting KC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-11 22:30:00</t>
+          <t>2026-10-15 00:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>11.00</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>7.18</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1690,42 +1650,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>St. Louis City vs LA Galaxy</t>
+          <t>Colorado Rapids vs Minnesota United</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-11 23:00:00</t>
+          <t>2026-10-15 01:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1739,89 +1699,51 @@
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
+      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Liga MX - MEX AL</t>
+          <t>Major League Soccer - USA MLS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Atlético San Luis vs Santos Laguna</t>
+          <t>Real Salt Lake vs SJ Earthquakes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-11 23:00:00</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
+          <t>2026-10-15 01:30:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2.37</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
+          <t>3.66</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -1831,63 +1753,61 @@
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Major League Soccer - USA MLS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Boyacá Chicó vs Cúcuta Deportivo</t>
+          <t>Los Angeles FC vs Austin</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-11 23:10:00</t>
+          <t>2026-10-15 02:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1899,91 +1819,103 @@
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Liga MX - MEX AL</t>
+          <t>Major League Soccer - USA MLS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pachuca vs Necaxa</t>
+          <t>LA Galaxy vs Portland Timbers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-11 23:10:00</t>
+          <t>2026-10-15 02:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>Major League Soccer - USA MLS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Talleres Córdoba vs Independiente</t>
+          <t>San Diego vs Houston Dynamo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-12 00:30:00</t>
+          <t>2026-10-15 02:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1993,37 +1925,37 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>3.00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -2035,375 +1967,357 @@
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Pro League - SAU PL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>América de Cali vs Independiente Medellín</t>
+          <t>Al Faisaly vs Al Kholood</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-12 01:15:00</t>
+          <t>2026-10-15 13:40:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
       <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Liga MX - MEX AL</t>
+          <t>Pro League - SAU PL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pumas UNAM vs Cruz Azul</t>
+          <t>Al Khaleej vs Al-Fayha</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-12 01:15:00</t>
+          <t>2026-10-15 14:50:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Pro League - SAU PL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Real Valladolid vs Albacete</t>
+          <t>Al Hazm vs Al Fateh</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-12 12:00:00</t>
+          <t>2026-10-15 15:15:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Pro League - SAU PL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Burgos vs Granada</t>
+          <t>Al Ahli vs Al Nassr</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-12 14:15:00</t>
+          <t>2026-10-15 18:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>3.74</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
           <t>2.37</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2.49</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>3.22</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Super League - GRC SL</t>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PAOK vs Kalamata</t>
+          <t>Huracán vs Gimnasia La Plata</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-12 15:00:00</t>
+          <t>2026-10-15 23:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -2415,267 +2329,307 @@
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Serie A - ITA SA</t>
+          <t>Pro League - SAU PL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Atalanta vs Venezia</t>
+          <t>Al-Qadsiah vs Abha</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-12 16:30:00</t>
+          <t>2026-10-16 13:15:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>14.64</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Pro League - SAU PL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Real Oviedo vs SD Eibar</t>
+          <t>Al Riyadh vs Al Hilal</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-12 16:30:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>13.97</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
       <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Superliga - DNK SL</t>
+          <t>2. Bundesliga - GER BII</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AGF vs Sønderjyske Fodbold</t>
+          <t>Energie Cottbus vs Nürnberg</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-12 17:00:00</t>
+          <t>2026-10-16 16:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
       <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Liga Portugal 2 - PRT SL</t>
+          <t>2. Bundesliga - GER BII</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Benfica II vs Felgueiras 1932</t>
+          <t>Holstein Kiel vs Hertha BSC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-12 17:00:00</t>
+          <t>2026-10-16 16:30:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2687,28 +2641,26 @@
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Super Lig - TUR SL</t>
+          <t>Superliga - DNK SL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Eyüpspor vs Göztepe</t>
+          <t>Horsens vs Randers FC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-12 17:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2718,100 +2670,114 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
       <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Serie A - ITA SA</t>
+          <t>Super Lig - TUR SL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Torino vs Udinese</t>
+          <t>Çorum FK vs Rizespor</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-12 18:45:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2823,139 +2789,127 @@
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>Eredivisie - NLD E</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Coritiba vs Botafogo</t>
+          <t>SC Heerenveen vs Excelsior</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-12 19:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>Pro League - SAU PL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lanús vs Vélez Sarsfield</t>
+          <t>Al Ittihad vs Al Shabab</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-12 19:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -2967,185 +2921,187 @@
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Premier League - UK PL</t>
+          <t>Bundesliga - GER BI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Coventry City vs Newcastle United</t>
+          <t>Eintracht Frankfurt vs FC Köln</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-12 19:00:00</t>
+          <t>2026-10-16 18:30:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
       <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
       <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>La Liga - ESP PL</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Levante vs Sevilla</t>
+          <t>Leganés vs Córdoba</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-12 19:00:00</t>
+          <t>2026-10-16 18:30:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
       <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Serie A - ITA SA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tenerife vs Girona</t>
+          <t>Frosinone vs Sassuolo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-12 19:00:00</t>
+          <t>2026-10-16 18:45:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3155,27 +3111,27 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -3187,149 +3143,109 @@
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Liga Portugal - PRT PL</t>
+          <t>Ligue 1 - FRA L1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Famalicão vs Alverca</t>
+          <t>Le Mans vs Toulouse</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-12 19:15:00</t>
+          <t>2026-10-16 18:45:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>2.06</t>
-        </is>
-      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>La Liga - ESP PL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gimnasia y Esgrima Mendoza vs Newell's Old Boys</t>
+          <t>Deportivo A Coruña vs Levante</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-12 21:30:00</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
+          <t>2026-10-16 19:00:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -3339,147 +3255,127 @@
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Chapecoense vs Athletico PR</t>
+          <t>Defensa y Justicia vs Instituto</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-12 22:30:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t>1.95</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>3.77</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>Primera Division - URY CL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bragantino vs Cruzeiro</t>
+          <t>Cerro vs Cerro Largo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-13 00:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -3487,227 +3383,213 @@
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga vs Rionegro Águilas</t>
+          <t>Mirassol vs Internacional</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-13 23:30:00</t>
+          <t>2026-10-16 23:00:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>4.04</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
       <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Millonarios vs Once Caldas</t>
+          <t>Boca Juniors vs Talleres Córdoba</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-14 01:30:00</t>
+          <t>2026-10-17 00:30:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Liga MX - MEX AL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Junior FC vs Deportivo Pereira</t>
+          <t>Necaxa vs Atlas</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-14 21:30:00</t>
+          <t>2026-10-17 01:00:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -3719,63 +3601,61 @@
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>Liga MX - MEX AL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sarmiento vs River Plate</t>
+          <t>Tijuana vs Puebla</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4.17</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t>1.70</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>5.33</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>3.53</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>2.20</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -3787,443 +3667,423 @@
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>Liga MX - MEX AL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Inter Miami vs New York City</t>
+          <t>Atlante vs Pumas UNAM</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-14 23:30:00</t>
+          <t>2026-10-17 03:00:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
+      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>J1 League - JPN JL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Columbus Crew vs Charlotte</t>
+          <t>Shimizu S-Pulse vs Gamba Osaka</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-14 23:30:00</t>
+          <t>2026-10-17 04:00:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
       <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>J1 League - JPN JL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cincinnati vs New England</t>
+          <t>Sanfrecce Hiroshima vs Kyoto Sanga</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-14 23:30:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
+      <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>J1 League - JPN JL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Toronto vs Orlando City</t>
+          <t>Tokyo Verdy vs FC Tokyo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-14 23:30:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
+      <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>J1 League - JPN JL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CF Montréal vs Atlanta United</t>
+          <t>JEF United vs Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-10-14 23:30:00</t>
+          <t>2026-10-17 05:00:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
       <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>J1 League - JPN JL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DC United vs New York RB</t>
+          <t>Cerezo Osaka vs Kawasaki Frontale</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-14 23:30:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -4235,279 +4095,275 @@
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>J1 League - JPN JL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Santa Fe vs Jaguares de Córdoba</t>
+          <t>Kashima Antlers vs V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-14 23:30:00</t>
+          <t>2026-10-17 06:00:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>1.86</t>
-        </is>
-      </c>
+      <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>J1 League - JPN JL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Dallas vs Seattle Sounders</t>
+          <t>Mito Hollyhock vs Urawa Reds</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-10-15 00:30:00</t>
+          <t>2026-10-17 07:00:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
       <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
       <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>K League 1 - KOR KL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Chicago Fire vs Philadelphia Union</t>
+          <t>Ulsan HD vs Bucheon 1995</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-15 00:30:00</t>
+          <t>2026-10-17 07:30:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
+      <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>J1 League - JPN JL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>St. Louis City vs Vancouver Whitecaps</t>
+          <t>Kashiwa Reysol vs Nagoya Grampus</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-15 00:30:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>4.36</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4.95</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -4519,149 +4375,105 @@
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>Super Lig - TUR SL</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nashville SC vs Sporting KC</t>
+          <t>Erzurumspor FK vs Eyüpspor</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-10-15 00:30:00</t>
+          <t>2026-10-17 10:30:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>1.86</t>
-        </is>
-      </c>
+      <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>Premier League - None</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Colorado Rapids vs Minnesota United</t>
+          <t>Krylya Sovetov vs Fakel</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-15 01:30:00</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>2.14</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>3.68</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>3.21</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>2.37</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
+          <t>2026-10-17 11:00:00</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
@@ -4671,45 +4483,63 @@
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>2. Bundesliga - GER BII</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Real Salt Lake vs SJ Earthquakes</t>
+          <t>SpVgg Greuther Fürth vs Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-15 01:30:00</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
+          <t>2026-10-17 11:00:00</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>3.48</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
@@ -4719,63 +4549,61 @@
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>2. Bundesliga - GER BII</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Los Angeles FC vs Austin</t>
+          <t>Kaiserslautern vs VfL Bochum 1848</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-15 02:30:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -4787,43 +4615,53 @@
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>2. Bundesliga - GER BII</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LA Galaxy vs Portland Timbers</t>
+          <t>VfL Wolfsburg vs FC Heidenheim</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-15 02:30:00</t>
+          <t>2026-10-17 11:00:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>3.96</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>4.79</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -4837,77 +4675,83 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
       <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Major League Soccer - USA MLS</t>
+          <t>Premier League - UK PL</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>San Diego vs Houston Dynamo</t>
+          <t>Everton vs Chelsea</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-15 02:30:00</t>
+          <t>2026-10-17 11:30:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -4919,157 +4763,219 @@
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Pro League - SAU PL</t>
+          <t>La Liga - ESP PL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Al Faisaly vs Al Kholood</t>
+          <t>Espanyol vs Atlético de Madrid</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-15 13:40:00</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
+          <t>2026-10-17 12:00:00</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
       <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
       <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Pro League - SAU PL</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Al Khaleej vs Al-Fayha</t>
+          <t>Real Sociedad II vs Almería</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-10-15 14:50:00</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
+          <t>2026-10-17 12:00:00</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>3.42</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
       <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Pro League - SAU PL</t>
+          <t>Serie A - ITA SA</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Al Hazm vs Al Fateh</t>
+          <t>Venezia vs Napoli</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-10-15 15:15:00</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
+          <t>2026-10-17 13:00:00</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2.37</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
@@ -5079,45 +4985,63 @@
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Pro League - SAU PL</t>
+          <t>Super Lig - TUR SL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Al Ahli vs Al Nassr</t>
+          <t>Gençlerbirliği vs Galatasaray</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-15 18:00:00</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
+          <t>2026-10-17 13:00:00</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2.04</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
@@ -5127,80 +5051,3642 @@
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>Super Lig - TUR SL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Huracán vs Gimnasia La Plata</t>
+          <t>Amed SK vs Konyaspor</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-15 23:00:00</t>
+          <t>2026-10-17 13:00:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Primera Division - URY CL</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Atlético Progreso vs Juventud</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-10-17 13:00:00</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Premier League - None</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Dynamo Makhachkala vs Akron</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-10-17 13:30:00</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Bundesliga - GER BI</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Elversberg vs FC Augsburg</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-10-17 13:30:00</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>3.77</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Bundesliga - GER BI</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Schalke 04 vs FSV Mainz 05</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-10-17 13:30:00</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>3.61</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Bundesliga - GER BI</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Werder Bremen vs Paderborn</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-10-17 13:30:00</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>4.18</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Bundesliga - GER BI</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Hamburger SV vs VfB Stuttgart</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-10-17 13:30:00</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Bundesliga - GER BI</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>FC Union Berlin vs Borussia Dortmund</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-10-17 13:30:00</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>4.85</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>4.42</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Premier League - UK PL</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Manchester City vs Ipswich Town</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-10-17 14:00:00</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>7.51</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>11.55</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Premier League - UK PL</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Fulham vs Hull City</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-10-17 14:00:00</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>4.78</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Premier League - UK PL</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Brentford vs Liverpool</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-10-17 14:00:00</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>3.63</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Super League - GRC SL</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Levadiakos vs Volos NFC</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-10-17 14:00:00</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>La Liga - ESP PL</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Villarreal vs Elche</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-10-17 14:15:00</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>5.04</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>6.41</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>La Liga 2 - ESP S</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SD Eibar vs Mallorca</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-10-17 14:15:00</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Eredivisie - NLD E</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>ADO Den Haag vs PSV</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-10-17 14:30:00</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>8.23</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>6.59</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Ligue 1 - FRA L1</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Strasbourg vs Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-10-17 15:15:00</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>6.30</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>5.46</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Pro League - SAU PL</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>NEOM SC vs Al Ettifaq</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-10-17 15:40:00</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>3.84</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Serie A - ITA SA</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Bologna vs Inter</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-10-17 16:00:00</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>5.99</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Super Lig - TUR SL</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Fenerbahçe vs Alanyaspor</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-10-17 16:00:00</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>5.57</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>8.86</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Primera Division - URY CL</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Racing vs Wanderers</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-10-17 16:00:00</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Premier League - UK PL</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Newcastle United vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-10-17 16:30:00</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>3.77</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Premier League - None</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Lokomotiv Moskva vs Krasnodar</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-10-17 16:30:00</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>La Liga - ESP PL</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Real Betis vs FC Barcelona</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-10-17 16:30:00</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>5.87</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>5.55</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Bundesliga - GER BI</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>FC Bayern München vs RB Leipzig</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-10-17 16:30:00</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>8.01</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>9.92</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>La Liga 2 - ESP S</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Sporting Gijón vs Albacete</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-10-17 16:30:00</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Super League - GRC SL</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Atromitos vs AEK Athens</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-10-17 16:30:00</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>6.33</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>4.43</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Banfield vs Argentinos Juniors</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-10-17 18:00:00</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>3.69</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Eredivisie - NLD E</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Telstar vs Feyenoord</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-10-17 18:00:00</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>8.03</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>5.36</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Pro League - SAU PL</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Al Diraiyah FC vs Al Taawoun</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-10-17 18:00:00</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>3.52</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>3.53</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Major League Soccer - USA MLS</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Philadelphia Union vs Charlotte</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-10-17 18:30:00</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2. Bundesliga - GER BII</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Hannover 96 vs St. Pauli</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-10-17 18:30:00</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Serie A - ITA SA</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Roma vs Genoa</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-10-17 18:45:00</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>5.10</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>7.77</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Ligue 1 - FRA L1</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Troyes vs Lens</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-10-17 18:45:00</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Ligue 1 - FRA L1</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>LOSC Lille vs Brest</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-10-17 18:45:00</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>3.97</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>4.19</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Eredivisie - NLD E</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Sparta Rotterdam vs Willem II</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-10-17 19:00:00</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>4.51</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>4.79</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>La Liga - ESP PL</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Valencia vs Athletic Club</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-10-17 19:00:00</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr"/>
+      <c r="T101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>La Liga 2 - ESP S</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Las Palmas vs Castellón</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-10-17 19:00:00</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>3.46</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>3.73</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Primera Division - URY CL</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Boston River vs Defensor Sporting</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-10-17 19:00:00</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
+      <c r="S103" t="inlineStr"/>
+      <c r="T103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Liga BetPlay - COL PA</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Boyacá Chicó vs Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-10-17 20:00:00</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>5.93</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr"/>
+      <c r="T104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Major League Soccer - USA MLS</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Minnesota United vs St. Louis City</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-10-17 20:30:00</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
+      <c r="S105" t="inlineStr"/>
+      <c r="T105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia vs Tigre</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-10-17 20:30:00</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>4.34</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
+      <c r="S106" t="inlineStr"/>
+      <c r="T106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Platense vs Lanús</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-10-17 20:30:00</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>2.84</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr"/>
+      <c r="S107" t="inlineStr"/>
+      <c r="T107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Serie A - BRA CB</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Botafogo vs Chapecoense</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-10-17 21:00:00</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>5.40</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>8.26</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
+      <c r="S108" t="inlineStr"/>
+      <c r="T108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Serie A - BRA CB</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro vs Coritiba</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-10-17 21:30:00</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>4.19</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>6.39</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
+      <c r="S109" t="inlineStr"/>
+      <c r="T109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Serie A - BRA CB</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Athletico PR vs Palmeiras</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-10-17 22:30:00</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Atlético Tucumán vs Rosario Central</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-10-17 23:00:00</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>2.97</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr"/>
+      <c r="S111" t="inlineStr"/>
+      <c r="T111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Vélez Sarsfield vs Gimnasia y Esgrima Mendoza</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-10-17 23:00:00</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>4.62</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr"/>
+      <c r="S112" t="inlineStr"/>
+      <c r="T112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Liga MX - MEX AL</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Santos Laguna vs Querétaro</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026-10-17 23:00:00</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr"/>
+      <c r="S113" t="inlineStr"/>
+      <c r="T113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Liga MX - MEX AL</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Guadalajara vs Tigres UANL</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026-10-17 23:07:00</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>3.53</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>4.44</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr"/>
+      <c r="T114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Major League Soccer - USA MLS</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Atlanta United vs Inter Miami</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2026-10-17 23:30:00</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr"/>
+      <c r="T115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Major League Soccer - USA MLS</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>New York City vs Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2026-10-17 23:30:00</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr"/>
+      <c r="T116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Major League Soccer - USA MLS</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>New York RB vs Toronto</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2026-10-17 23:30:00</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr"/>
+      <c r="T117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Major League Soccer - USA MLS</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Orlando City vs DC United</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2026-10-17 23:30:00</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr"/>
+      <c r="S118" t="inlineStr"/>
+      <c r="T118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Major League Soccer - USA MLS</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>New England vs Chicago Fire</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2026-10-17 23:30:00</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr"/>
+      <c r="S119" t="inlineStr"/>
+      <c r="T119" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
